--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_842_Hawaii_Main_Islands_USA.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_842_Hawaii_Main_Islands_USA.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc64ed1f8c33f44e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R19c97b0fb093406c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R44c7cbd1c3fb46e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc99c80c07ab94d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R84e838eca2c04085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re8fa5a9bacd6434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rae131e65a399406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re8a13c29a3a54613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rcb9f07575d6a4265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R54613d04048b4d28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8e182fb585974a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R440224c5e4554e88"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ842CommercialTable" displayName="EEZ842CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ842CommercialTable" displayName="EEZ842CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ842FunctionalTable" displayName="EEZ842FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ842FunctionalTable" displayName="EEZ842FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ842ValidationTable" displayName="EEZ842ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ842ValidationTable" displayName="EEZ842ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10074,7 +10028,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70e082b6aa3d4ce4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c0475444fd640d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10084,20 +10038,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10105,552 +10049,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3.7108435920999994</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.371441144088203</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>235.20207241883924</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3.7108435920999994</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>412.7096933909512</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$141,A2,'Species'!$U$2:$U$141))</x:f>
-        <x:v>1531.5011211173667</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.371441144088203</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>235.20207241883924</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>872.7981032840896</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>658.703017833277</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.7547026229259275</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.7547026229259275</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.5739948661</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.3654870900525635</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2319.9952197808457</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.5739948661</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2355.770277725424</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$141,A3,'Species'!$U$2:$U$141))</x:f>
-        <x:v>1352.2000451253643</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.3654870900525635</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2319.9952197808457</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1331.6653455307464</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>20.534699594617905</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0154203153694246</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.015420315369424611</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>40.7497878284</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.566943517773209</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>368.92961425970685</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>40.7497878284</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>369.84304683511385</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$141,A4,'Species'!$U$2:$U$141))</x:f>
-        <x:v>15071.025688339894</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.566943517773209</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>368.92961425970685</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15033.80350469651</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>37.22218364338369</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0024758993046408</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.002475899304640745</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5.3260879421</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5.3260879421</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>114.8153621496883</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$141,A5,'Species'!$U$2:$U$141))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>611.5167159132995</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>611.5167159132995</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1608.5046165551998</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.6314344331671733</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>427.9907995627233</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1608.5046165551998</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>774.3523836380311</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$141,A6,'Species'!$U$2:$U$141))</x:f>
-        <x:v>1245549.3839222963</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.6314344331671733</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>427.9907995627233</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>688425.1769397917</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>557124.2069825047</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.8092734339831236</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.8092734339831237</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>12850.291446256002</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.205720779439804</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1605.9084357697302</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>12850.291446256002</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1902.1344268699645</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$141,A7,'Species'!$U$2:$U$141))</x:f>
-        <x:v>24442981.755236167</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.205720779439804</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1605.9084357697302</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>20636391.43564212</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3806590.319594048</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1844600753705175</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.18446007537051753</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>5.4123992603</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9118433997421773</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>816.2879767422801</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>5.4123992603</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>819.343567185262</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$141,A8,'Species'!$U$2:$U$141))</x:f>
-        <x:v>4434.614516965075</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9118433997421773</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>816.2879767422801</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4418.0764415117</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>16.538075453375313</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0037432750818853</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.00374327508188532</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>301.2882327891999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.2355911944412306</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1720.248526194656</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>301.2882327891999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1820.8958829621845</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$141,A9,'Species'!$U$2:$U$141))</x:f>
-        <x:v>548614.5026708064</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.2355911944412306</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1720.248526194656</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>518290.6384154136</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>30323.86425539275</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.058507451240298</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.05850745124029803</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>7670.3291661178</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.441269625296016</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2762.292252214383</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>7670.3291661178</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2776.397969613466</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$141,A10,'Species'!$U$2:$U$141))</x:f>
-        <x:v>21295886.323076412</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.441269625296016</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2762.292252214383</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>21187690.827501208</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>108195.49557520449</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0051065260700693</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.005106526070069366</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra01cd32202464c83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11aeb3f3e5314513"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10660,20 +10245,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10681,1200 +10256,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5.8499877529</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6562999146960147</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>453.2104495286419</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>5.8499877529</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>464.03095235262424</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$141,A2,'Species'!$U$2:$U$141))</x:f>
-        <x:v>2714.575388229375</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6562999146960147</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>453.2104495286419</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2651.2755792288585</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>63.29980900051669</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0238752280209693</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.023875228020969388</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>77.0308251526</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.42</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2630.2679918953813</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>77.0308251526</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$141,A3,'Species'!$U$2:$U$141))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>202611.71378817345</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.42</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2630.2679918953813</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>202611.71378817345</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>630.8398632888</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.22</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1659.5869074375596</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>630.8398632888</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1659.5869074375596</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$141,A4,'Species'!$U$2:$U$141))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1046933.5778037924</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.22</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1659.5869074375596</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>1046933.5778037924</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>161.61179304610002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.480978527686107</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>302.67637756621025</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>161.61179304610002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1026.5761579480786</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$141,A5,'Species'!$U$2:$U$141))</x:f>
-        <x:v>165906.81358436536</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.480978527686107</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>302.67637756621025</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>48916.0720911736</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>116990.74149319176</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>3.3916626272676855</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>2.3916626272676855</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>72.03158193269999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.49</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3090.295432513592</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>72.03158193269999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$141,A6,'Species'!$U$2:$U$141))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>222598.86864335136</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.49</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>222598.86864335136</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>16047.7748049613</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.363992851893965</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2312.0267359313875</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>16047.7748049613</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2359.847744005312</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$141,A7,'Species'!$U$2:$U$141))</x:f>
-        <x:v>37870305.16979321</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.363992851893965</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2312.0267359313875</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>37102884.40127663</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>767420.7685165778</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0206835878369114</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.020683587836911474</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1.4648299929</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.36</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>229.08676527677724</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1.4648299929</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$141,A8,'Species'!$U$2:$U$141))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>335.57316475386557</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.36</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>335.57316475386557</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1720.0154630335003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.451920302737462</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2830.8724554942733</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1720.0154630335003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2889.1389789693594</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$141,A9,'Species'!$U$2:$U$141))</x:f>
-        <x:v>4969363.718680117</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.451920302737462</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2830.8724554942733</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4869144.397325764</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>100219.32135435287</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0205825322020425</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.020582532202042602</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>299.82340279629994</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.239869020091846</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1737.2768002799908</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>299.82340279629994</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1828.6728934183743</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$141,A10,'Species'!$U$2:$U$141))</x:f>
-        <x:v>548278.9295060525</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.239869020091846</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1737.2768002799908</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>520876.2418590148</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>27402.687647037732</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.052608826137351</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.052608826137351065</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>2.6997849970999996</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.697792338614222</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>498.645998867788</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>2.6997849970999996</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>555.4252070617486</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$141,A11,'Species'!$U$2:$U$141))</x:f>
-        <x:v>1499.5286410364695</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.697792338614222</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>498.645998867788</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1346.2369866071974</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>153.29165442927206</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.11386676785311</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.11386676785310997</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>21.5021196912</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.6700000000000004</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>467.7351412871986</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>21.5021196912</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>467.73514128719813</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$141,A12,'Species'!$U$2:$U$141))</x:f>
-        <x:v>10057.296991737678</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.6700000000000004</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>467.7351412871986</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>10057.296991737687</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>-9.094947017729282e-12</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>-9.043132588409193e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.0352779982</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.4910323168223303</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>309.7649793679956</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.0352779982</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>363.2121756308457</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$141,A13,'Species'!$U$2:$U$141))</x:f>
-        <x:v>12.813398478123059</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.4910323168223303</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>309.7649793679956</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>10.927888384567185</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1.8855100935558742</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.172541119308893</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.17254111930889315</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>304.88671568150005</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.0888568245328365</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1227.0346434246292</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>304.88671568150005</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1227.8183902644819</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$141,A14,'Species'!$U$2:$U$141))</x:f>
-        <x:v>374345.5164610842</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.0888568245328365</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1227.0346434246292</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>374106.5624611557</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>238.9539999284898</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0006387324465962</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.000638732446596151</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1089.0117543435</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.499084402384975</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>315.5617838148181</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1089.0117543435</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>525.0445673955084</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$141,A15,'Species'!$U$2:$U$141))</x:f>
-        <x:v>571779.7054479065</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.499084402384975</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>315.5617838148181</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>343650.49179593934</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>228129.21365196718</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.6638407891103237</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.6638407891103236</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>967.0737393424001</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.982280465597428</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>960.0204086170238</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>967.0737393424001</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1179.6873935280641</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$141,A16,'Species'!$U$2:$U$141))</x:f>
-        <x:v>1140844.6989142746</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.982280465597428</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>960.0204086170238</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>928410.5264062842</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>212434.17250799038</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2288149115782714</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.22881491157827147</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>867.3429174956999</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3127574167274267</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>205.47425606543015</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>867.3429174956999</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>443.57216977197675</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$141,A17,'Species'!$U$2:$U$141))</x:f>
-        <x:v>384729.1798499242</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3127574167274267</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>205.47425606543015</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>178216.6407260487</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>206512.53912387553</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.1587724820900576</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.1587724820900578</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>5.3260879421</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>5.3260879421</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>114.8153621496883</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$141,A18,'Species'!$U$2:$U$141))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>611.5167159132995</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>611.5167159132995</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1.011058595</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1.011058595</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$141,A19,'Species'!$U$2:$U$141))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>31.972480080897288</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>31.972480080897288</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>40.7497878284</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.566943517773209</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>368.92961425970685</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>40.7497878284</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>369.84304683511385</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$141,A20,'Species'!$U$2:$U$141))</x:f>
-        <x:v>15071.025688339894</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.566943517773209</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>368.92961425970685</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>15033.80350469651</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>37.22218364338369</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0024758993046408</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.002475899304640745</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>169.53078446889998</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.0240554542067675</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>105.69524607749835</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>169.53078446889998</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>157.18931573794987</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$141,A21,'Species'!$U$2:$U$141))</x:f>
-        <x:v>26648.428007184248</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.0240554542067675</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>105.69524607749835</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>17918.59798215172</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>8729.830025032526</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.487193810237168</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.48719381023716796</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>0.5739948661</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>4.3654870900525635</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>2319.9952197808457</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>0.5739948661</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>2355.770277725424</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$141,A22,'Species'!$U$2:$U$141))</x:f>
-        <x:v>1352.2000451253643</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>4.3654870900525635</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>2319.9952197808457</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1331.6653455307464</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>20.534699594617905</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0154203153694246</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.015420315369424611</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57a3c4e3ee454bd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e53207aae8d4e44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12049,7 +10845,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -12148,7 +10944,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>47556032.822993144</x:v>
+        <x:v>43053065.938609466</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12162,7 +10958,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>47556032.82299315</x:v>
+        <x:v>45887678.36081641</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12176,7 +10972,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4502966.884383678</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12190,7 +10986,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>7.450580596923828e-9</x:v>
+        <x:v>-1668354.4621767327</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -12201,9 +10997,9 @@
         <x:v>EEZ_842</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -12215,47 +11011,19 @@
         <x:v>EEZ_842</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_842</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_842</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a965bfc63a14b79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97e69039c5114325"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12302,7 +11070,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
